--- a/Intersecciones/excels/JUNIN-CHANCHAMAYO-CHANCHAMAYO.xlsx
+++ b/Intersecciones/excels/JUNIN-CHANCHAMAYO-CHANCHAMAYO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,266 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-207740</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>120302</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PERENE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-10.9499854</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-75.2255441</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>120301</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-609182</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>120302</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PERENE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-10.9962807</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-75.0520952</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>120301</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-615541</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PICHANAQUI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-10.9212072</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-74.7307326</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>120301</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-615544</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PICHANAQUI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-10.9173554</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-74.7261903</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>120301</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-615536</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PICHANAQUI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-10.9364737</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-74.7037911</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>120301</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
